--- a/socks_results_thresholds.xlsx
+++ b/socks_results_thresholds.xlsx
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -518,109 +518,109 @@
         </is>
       </c>
       <c r="B2" s="4" t="n">
-        <v>-0.2161895000000001</v>
+        <v>-0.2180952999999999</v>
       </c>
       <c r="C2" s="4" t="n">
         <v>-0.05849459999999992</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>-0.02340942494859838</v>
+        <v>-0.02702979717376034</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>-0.1013223663796775</v>
+        <v>-0.1452722304197982</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>0.07924466923691052</v>
+        <v>0.09328141709018822</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>-0.1387102019213195</v>
+        <v>-0.1019690625122296</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>0.02047550553090839</v>
+        <v>0.01713919321144639</v>
       </c>
       <c r="I2" s="3" t="inlineStr"/>
     </row>
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>002624</t>
+          <t>000977</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>0.2157097000000001</v>
+        <v>0.4230446999999999</v>
       </c>
       <c r="C3" s="4" t="n">
-        <v>0.1070351999999999</v>
+        <v>0.0262837999999999</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>-0.006364657600770026</v>
+        <v>-0.1066747813811346</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>-0.02213203346614372</v>
+        <v>0.1498832031057415</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>-0.0610185913689125</v>
+        <v>0.2330901106022669</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>0.1010004851437114</v>
+        <v>0.1082244205513318</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>0.09324298136322011</v>
+        <v>-0.01220866190130745</v>
       </c>
       <c r="I3" s="3" t="inlineStr"/>
     </row>
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>002714</t>
+          <t>002094</t>
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>0.2741978999999999</v>
+        <v>0.1295256999999999</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>0.08721649999999995</v>
+        <v>0.05117239999999991</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>0.02693814893353817</v>
+        <v>0.03629271468695326</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0.00129296435185505</v>
+        <v>-0.02754832063935526</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>0.04138476245355669</v>
+        <v>-0.0521059256029355</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>0.1039602952619436</v>
+        <v>0.124677029604524</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>-0.008595866144504501</v>
+        <v>0.0001935700218303342</v>
       </c>
       <c r="I4" s="3" t="inlineStr"/>
     </row>
     <row r="5" ht="20" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>600063</t>
+          <t>002555</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>0.0257137999999999</v>
+        <v>0.05284090000000008</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>0.002690899999999966</v>
+        <v>0.2831592999999999</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>0.03350234853033971</v>
+        <v>-0.1304498981537211</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>-0.06354120890096279</v>
+        <v>-0.09090303720843149</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>0.05696105681081508</v>
+        <v>-0.07758874378255967</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>0</v>
+        <v>0.1252596878337947</v>
       </c>
       <c r="H5" s="4" t="n">
         <v>0</v>
@@ -630,147 +630,292 @@
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>600875</t>
+          <t>002594</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>0.3681178999999999</v>
+        <v>-0.06441399999999964</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>0.105315</v>
+        <v>0.00018</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.1127092276862252</v>
+        <v>0.1546310664080468</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-0.1023645773758425</v>
+        <v>-0.09704245328071308</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.07288591287328242</v>
+        <v>0.1142473823338885</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.1550538877384371</v>
+        <v>-0.15376679473516</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0</v>
+        <v>-0.04846823060853792</v>
       </c>
       <c r="I6" s="3" t="inlineStr"/>
     </row>
     <row r="7" ht="20" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>600887</t>
+          <t>002624</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>0.06084289999999992</v>
+        <v>0.08249399999999962</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>0.07508529999999999</v>
+        <v>0.1553373999999999</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-0.00914904147605768</v>
+        <v>-0.1311731101235016</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-0.05809635359535093</v>
+        <v>-0.05510325783865572</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>0.05207272109712722</v>
+        <v>-0.05307175867986984</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0.00895756955693857</v>
+        <v>0.1024729025766504</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.003964825831871206</v>
+        <v>0.09323635911190532</v>
       </c>
       <c r="I7" s="3" t="inlineStr"/>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>603083</t>
+          <t>002714</t>
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>0.4997150000000004</v>
+        <v>0.2337103000000003</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>0.01129989999999991</v>
+        <v>0.09418869999999996</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.2494918668537397</v>
+        <v>0.03616213547078312</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.1499197933541254</v>
+        <v>0.00132250573293108</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.1956002896001536</v>
+        <v>0.03106972407904722</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.1698199798984458</v>
+        <v>0.06312542267235897</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.001770529994175888</v>
+        <v>-0.008604982969957507</v>
       </c>
       <c r="I8" s="3" t="inlineStr"/>
     </row>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>603128</t>
+          <t>600063</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>-0.05158479999999999</v>
+        <v>0.0458381000000001</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>0.05582559999999998</v>
+        <v>0.002690899999999966</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>0.01077810577807557</v>
+        <v>0.05377110732729315</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-0.08288601238337061</v>
+        <v>-0.06353830616444131</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.05343739814804415</v>
+        <v>0.05696615678851653</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.02602199024402041</v>
+        <v>0</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.002251315862561164</v>
+        <v>0</v>
       </c>
       <c r="I9" s="3" t="inlineStr"/>
     </row>
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
+          <t>600498</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="n">
+        <v>0.4654414000000002</v>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>0.001562400000000052</v>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>-0.04040297439280868</v>
+      </c>
+      <c r="E10" s="4" t="n">
+        <v>0.04134216311102202</v>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>0.1677680357535211</v>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v>0.2141658168892346</v>
+      </c>
+      <c r="H10" s="4" t="n">
+        <v>0.03269842097585628</v>
+      </c>
+      <c r="I10" s="3" t="inlineStr"/>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>600875</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="n">
+        <v>0.2977320000000001</v>
+      </c>
+      <c r="C11" s="4" t="n">
+        <v>0.105315</v>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>0.1127092276862252</v>
+      </c>
+      <c r="E11" s="4" t="n">
+        <v>-0.1023645773758425</v>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>0.05094599023221628</v>
+      </c>
+      <c r="G11" s="4" t="n">
+        <v>0.1185022971093588</v>
+      </c>
+      <c r="H11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="3" t="inlineStr"/>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>600887</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="n">
+        <v>0.01467790000000013</v>
+      </c>
+      <c r="C12" s="4" t="n">
+        <v>0.07508529999999999</v>
+      </c>
+      <c r="D12" s="4" t="n">
+        <v>-0.00914904147605768</v>
+      </c>
+      <c r="E12" s="4" t="n">
+        <v>-0.05809635359535093</v>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>0.04580728674052106</v>
+      </c>
+      <c r="G12" s="4" t="n">
+        <v>-0.01264767252425009</v>
+      </c>
+      <c r="H12" s="4" t="n">
+        <v>-0.02063033515692266</v>
+      </c>
+      <c r="I12" s="3" t="inlineStr"/>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>603083</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="n">
+        <v>0.5211780000000001</v>
+      </c>
+      <c r="C13" s="4" t="n">
+        <v>0.01129989999999991</v>
+      </c>
+      <c r="D13" s="4" t="n">
+        <v>0.2494918668537397</v>
+      </c>
+      <c r="E13" s="4" t="n">
+        <v>-0.1499197933541254</v>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>0.1196271691268436</v>
+      </c>
+      <c r="G13" s="4" t="n">
+        <v>0.2670766819213272</v>
+      </c>
+      <c r="H13" s="4" t="n">
+        <v>-0.001770485262580534</v>
+      </c>
+      <c r="I13" s="3" t="inlineStr"/>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>603128</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="n">
+        <v>-0.09831159999999993</v>
+      </c>
+      <c r="C14" s="4" t="n">
+        <v>0.05582559999999998</v>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>-0.02013609065739635</v>
+      </c>
+      <c r="E14" s="4" t="n">
+        <v>-0.0839894703611777</v>
+      </c>
+      <c r="F14" s="4" t="n">
+        <v>-0.0393859568407999</v>
+      </c>
+      <c r="G14" s="4" t="n">
+        <v>-0.006888136600099408</v>
+      </c>
+      <c r="H14" s="4" t="n">
+        <v>-0.002642252232442148</v>
+      </c>
+      <c r="I14" s="3" t="inlineStr"/>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
           <t>603496</t>
         </is>
       </c>
-      <c r="B10" s="4" t="n">
-        <v>1.236649</v>
-      </c>
-      <c r="C10" s="4" t="n">
+      <c r="B15" s="4" t="n">
+        <v>1.5948434</v>
+      </c>
+      <c r="C15" s="4" t="n">
         <v>0.0361725</v>
       </c>
-      <c r="D10" s="4" t="n">
-        <v>0.09471830221319325</v>
-      </c>
-      <c r="E10" s="4" t="n">
-        <v>0.3172648386650292</v>
-      </c>
-      <c r="F10" s="4" t="n">
-        <v>0.149325265850348</v>
-      </c>
-      <c r="G10" s="4" t="n">
-        <v>0.2714941230131585</v>
-      </c>
-      <c r="H10" s="4" t="n">
-        <v>0.02431370516000797</v>
-      </c>
-      <c r="I10" s="3" t="inlineStr"/>
+      <c r="D15" s="4" t="n">
+        <v>0.2171775452446383</v>
+      </c>
+      <c r="E15" s="4" t="n">
+        <v>0.4721239410630732</v>
+      </c>
+      <c r="F15" s="4" t="n">
+        <v>0.1493037949935029</v>
+      </c>
+      <c r="G15" s="4" t="n">
+        <v>0.1871732236914713</v>
+      </c>
+      <c r="H15" s="4" t="n">
+        <v>0.02431103228242936</v>
+      </c>
+      <c r="I15" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/socks_results_thresholds.xlsx
+++ b/socks_results_thresholds.xlsx
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:N27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -461,7 +461,12 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="25" customHeight="1">
@@ -477,35 +482,60 @@
       </c>
       <c r="C1" s="2" t="inlineStr">
         <is>
+          <t>2016年收益率</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>2017年收益率</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>2018年收益率</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>2019年收益率</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>2020年收益率</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
           <t>2021年收益率</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="I1" s="2" t="inlineStr">
         <is>
           <t>2022年收益率</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>2023年收益率</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="K1" s="2" t="inlineStr">
         <is>
           <t>2024年收益率</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="L1" s="2" t="inlineStr">
         <is>
           <t>2025年收益率</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="M1" s="2" t="inlineStr">
         <is>
           <t>2026年收益率</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>gittag</t>
         </is>
@@ -518,404 +548,1142 @@
         </is>
       </c>
       <c r="B2" s="4" t="n">
-        <v>-0.2180952999999999</v>
+        <v>-0.02688516057819335</v>
       </c>
       <c r="C2" s="4" t="n">
-        <v>-0.05849459999999992</v>
+        <v>-0.001229430484744371</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>-0.02702979717376034</v>
+        <v>0.1656643334342487</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>-0.1452722304197982</v>
+        <v>-0.003593012108475397</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>0.09328141709018822</v>
+        <v>0.1140605089202705</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>-0.1019690625122296</v>
+        <v>0.04428120901698484</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>0.01713919321144639</v>
-      </c>
-      <c r="I2" s="3" t="inlineStr"/>
+        <v>-0.0468806028697747</v>
+      </c>
+      <c r="I2" s="4" t="n">
+        <v>-0.0247695834862358</v>
+      </c>
+      <c r="J2" s="4" t="n">
+        <v>-0.180405286018933</v>
+      </c>
+      <c r="K2" s="4" t="n">
+        <v>0.05392040847239359</v>
+      </c>
+      <c r="L2" s="4" t="n">
+        <v>-0.1019503797811989</v>
+      </c>
+      <c r="M2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" s="3" t="inlineStr"/>
     </row>
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>000977</t>
+          <t>000519</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>0.4230446999999999</v>
+        <v>0.377496137029351</v>
       </c>
       <c r="C3" s="4" t="n">
-        <v>0.0262837999999999</v>
+        <v>0.01318246158557915</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>-0.1066747813811346</v>
+        <v>-0.0952530584894674</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>0.1498832031057415</v>
+        <v>-0.1563864246971372</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>0.2330901106022669</v>
+        <v>0.205478441365287</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>0.1082244205513318</v>
+        <v>0.1465861162792758</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>-0.01220866190130745</v>
-      </c>
-      <c r="I3" s="3" t="inlineStr"/>
+        <v>0.0271042607160982</v>
+      </c>
+      <c r="I3" s="4" t="n">
+        <v>0.1379741129790851</v>
+      </c>
+      <c r="J3" s="4" t="n">
+        <v>-0.08908726175306908</v>
+      </c>
+      <c r="K3" s="4" t="n">
+        <v>0.04976037528529616</v>
+      </c>
+      <c r="L3" s="4" t="n">
+        <v>0.1138387274401325</v>
+      </c>
+      <c r="M3" s="4" t="n">
+        <v>0.0352130490992859</v>
+      </c>
+      <c r="N3" s="3" t="inlineStr"/>
     </row>
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>002094</t>
+          <t>000977</t>
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>0.1295256999999999</v>
+        <v>1.143698460469436</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>0.05117239999999991</v>
+        <v>-0.01494098093198118</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>0.03629271468695326</v>
+        <v>0.01004849813436328</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>-0.02754832063935526</v>
+        <v>0.111625921258592</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>-0.0521059256029355</v>
+        <v>0.5171515276114548</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>0.124677029604524</v>
+        <v>-0.105986385194218</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>0.0001935700218303342</v>
-      </c>
-      <c r="I4" s="3" t="inlineStr"/>
+        <v>0.1330178214616553</v>
+      </c>
+      <c r="I4" s="4" t="n">
+        <v>-0.1018644865278034</v>
+      </c>
+      <c r="J4" s="4" t="n">
+        <v>0.03643743922935658</v>
+      </c>
+      <c r="K4" s="4" t="n">
+        <v>0.2353095035440132</v>
+      </c>
+      <c r="L4" s="4" t="n">
+        <v>0.1089321108997107</v>
+      </c>
+      <c r="M4" s="4" t="n">
+        <v>-0.01093458577464405</v>
+      </c>
+      <c r="N4" s="3" t="inlineStr"/>
     </row>
     <row r="5" ht="20" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>002555</t>
+          <t>002094</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>0.05284090000000008</v>
+        <v>-0.2290302956447963</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>0.2831592999999999</v>
+        <v>0</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>-0.1304498981537211</v>
+        <v>-0.1301937625754147</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>-0.09090303720843149</v>
+        <v>-0.1838798414954443</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>-0.07758874378255967</v>
+        <v>0.01404220477612879</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>0.1252596878337947</v>
+        <v>-0.08051915243196768</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" s="3" t="inlineStr"/>
+        <v>0.09785830979487793</v>
+      </c>
+      <c r="I5" s="4" t="n">
+        <v>0.03629962329816265</v>
+      </c>
+      <c r="J5" s="4" t="n">
+        <v>-0.02755302360837973</v>
+      </c>
+      <c r="K5" s="4" t="n">
+        <v>-0.05212087595361039</v>
+      </c>
+      <c r="L5" s="4" t="n">
+        <v>0.1246789207831454</v>
+      </c>
+      <c r="M5" s="4" t="n">
+        <v>-0.01239587949989335</v>
+      </c>
+      <c r="N5" s="3" t="inlineStr"/>
     </row>
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>002594</t>
+          <t>002432</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>-0.06441399999999964</v>
+        <v>0.3110604900449792</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>0.00018</v>
+        <v>-0.003567645467814582</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.1546310664080468</v>
+        <v>-0.1290132091389888</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-0.09704245328071308</v>
+        <v>-0.1880559408811423</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.1142473823338885</v>
+        <v>0.1159530934774647</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.15376679473516</v>
+        <v>0.06126171057603467</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.04846823060853792</v>
-      </c>
-      <c r="I6" s="3" t="inlineStr"/>
+        <v>0.5225839775838861</v>
+      </c>
+      <c r="I6" s="4" t="n">
+        <v>0.003203079575666372</v>
+      </c>
+      <c r="J6" s="4" t="n">
+        <v>-0.05280577633166925</v>
+      </c>
+      <c r="K6" s="4" t="n">
+        <v>0.06032220974427589</v>
+      </c>
+      <c r="L6" s="4" t="n">
+        <v>0.02405146832768522</v>
+      </c>
+      <c r="M6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="3" t="inlineStr"/>
     </row>
     <row r="7" ht="20" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>002624</t>
+          <t>002555</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>0.08249399999999962</v>
+        <v>-0.2188510394624068</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>0.1553373999999999</v>
+        <v>0</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-0.1311731101235016</v>
+        <v>0.09099950751456025</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-0.05510325783865572</v>
+        <v>-0.2377656542307907</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.05307175867986984</v>
+        <v>0.2779628499867827</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0.1024729025766504</v>
+        <v>-0.02543797340634396</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>0.09323635911190532</v>
-      </c>
-      <c r="I7" s="3" t="inlineStr"/>
+        <v>-0.09961789237374166</v>
+      </c>
+      <c r="I7" s="4" t="n">
+        <v>-0.1035074899688088</v>
+      </c>
+      <c r="J7" s="4" t="n">
+        <v>-0.08671502997329111</v>
+      </c>
+      <c r="K7" s="4" t="n">
+        <v>-0.04581770165777979</v>
+      </c>
+      <c r="L7" s="4" t="n">
+        <v>0.07221502508590945</v>
+      </c>
+      <c r="M7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" s="3" t="inlineStr"/>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>002714</t>
+          <t>002624</t>
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>0.2337103000000003</v>
+        <v>0.4268999207145161</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>0.09418869999999996</v>
+        <v>-0.0284554010545573</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.03616213547078312</v>
+        <v>0.09582701881215398</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.00132250573293108</v>
+        <v>-0.005636468121785037</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.03106972407904722</v>
+        <v>0.1344483265075544</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.06312542267235897</v>
+        <v>0.1015726439376286</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.008604982969957507</v>
-      </c>
-      <c r="I8" s="3" t="inlineStr"/>
+        <v>-0.1108238055538835</v>
+      </c>
+      <c r="I8" s="4" t="n">
+        <v>0.0704027897791301</v>
+      </c>
+      <c r="J8" s="4" t="n">
+        <v>-0.03811981024071829</v>
+      </c>
+      <c r="K8" s="4" t="n">
+        <v>-0.02329686757931304</v>
+      </c>
+      <c r="L8" s="4" t="n">
+        <v>0.1024858528982778</v>
+      </c>
+      <c r="M8" s="4" t="n">
+        <v>0.09409258056649271</v>
+      </c>
+      <c r="N8" s="3" t="inlineStr"/>
     </row>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>600063</t>
+          <t>002714</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>0.0458381000000001</v>
+        <v>0.8926070977009466</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>0.002690899999999966</v>
+        <v>-0.01066519190672829</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>0.05377110732729315</v>
+        <v>0.06766153381903181</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-0.06353830616444131</v>
+        <v>0.08031996929812378</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.05696615678851653</v>
+        <v>0.15982980424429</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0</v>
+        <v>0.1288910218602991</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" s="3" t="inlineStr"/>
+        <v>0.0999505012702567</v>
+      </c>
+      <c r="I9" s="4" t="n">
+        <v>0.0371147743460891</v>
+      </c>
+      <c r="J9" s="4" t="n">
+        <v>0.007062825395437806</v>
+      </c>
+      <c r="K9" s="4" t="n">
+        <v>0.03956762151624565</v>
+      </c>
+      <c r="L9" s="4" t="n">
+        <v>0.06696155756677309</v>
+      </c>
+      <c r="M9" s="4" t="n">
+        <v>-0.005907386072839737</v>
+      </c>
+      <c r="N9" s="3" t="inlineStr"/>
     </row>
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>600498</t>
+          <t>300454</t>
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>0.4654414000000002</v>
+        <v>0.1934996039077262</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.001562400000000052</v>
+        <v>0</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.04040297439280868</v>
+        <v>0</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.04134216311102202</v>
+        <v>0.09097464452620072</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.1677680357535211</v>
+        <v>0.1655050880738232</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.2141658168892346</v>
+        <v>0.030559663258263</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>0.03269842097585628</v>
-      </c>
-      <c r="I10" s="3" t="inlineStr"/>
+        <v>-0.04881845592860357</v>
+      </c>
+      <c r="I10" s="4" t="n">
+        <v>-0.1862046625158259</v>
+      </c>
+      <c r="J10" s="4" t="n">
+        <v>-0.1270161084898588</v>
+      </c>
+      <c r="K10" s="4" t="n">
+        <v>0.00357149884562849</v>
+      </c>
+      <c r="L10" s="4" t="n">
+        <v>0.316062217833205</v>
+      </c>
+      <c r="M10" s="4" t="n">
+        <v>0.02049463431685845</v>
+      </c>
+      <c r="N10" s="3" t="inlineStr"/>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>600875</t>
+          <t>302132</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>0.2977320000000001</v>
+        <v>1.343704051553807</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.105315</v>
+        <v>-0.004378971714252547</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.1127092276862252</v>
+        <v>-0.1288202016352762</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-0.1023645773758425</v>
+        <v>-0.03806863730051115</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.05094599023221628</v>
+        <v>0.2956342080951972</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0.1185022971093588</v>
+        <v>0.093663066087303</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" s="3" t="inlineStr"/>
+        <v>0.08888623741099157</v>
+      </c>
+      <c r="I11" s="4" t="n">
+        <v>-0.1006717304009044</v>
+      </c>
+      <c r="J11" s="4" t="n">
+        <v>0.2614577983040718</v>
+      </c>
+      <c r="K11" s="4" t="n">
+        <v>0.2311750258341424</v>
+      </c>
+      <c r="L11" s="4" t="n">
+        <v>0.2873415630261882</v>
+      </c>
+      <c r="M11" s="4" t="n">
+        <v>0.01252046329634601</v>
+      </c>
+      <c r="N11" s="3" t="inlineStr"/>
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>600887</t>
+          <t>600063</t>
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>0.01467790000000013</v>
+        <v>0.4326360890943335</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.07508529999999999</v>
+        <v>0.01088949595447804</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-0.00914904147605768</v>
+        <v>-0.03884673095519597</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.05809635359535093</v>
+        <v>-0.170216633932247</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.04580728674052106</v>
+        <v>0.2692628084621347</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.01264767252425009</v>
+        <v>0.07089827004186536</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.02063033515692266</v>
-      </c>
-      <c r="I12" s="3" t="inlineStr"/>
+        <v>0.2309421280662373</v>
+      </c>
+      <c r="I12" s="4" t="n">
+        <v>0.05715122761087535</v>
+      </c>
+      <c r="J12" s="4" t="n">
+        <v>-0.05593706866886022</v>
+      </c>
+      <c r="K12" s="4" t="n">
+        <v>0.06414145097815074</v>
+      </c>
+      <c r="L12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" s="3" t="inlineStr"/>
     </row>
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>603083</t>
+          <t>600089</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>0.5211780000000001</v>
+        <v>0.3042690707426874</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.01129989999999991</v>
+        <v>0</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.2494918668537397</v>
+        <v>0.01176426661526828</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-0.1499197933541254</v>
+        <v>-0.05403457753494112</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.1196271691268436</v>
+        <v>0.06755490035253181</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.2670766819213272</v>
+        <v>0.08749726691733965</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.001770485262580534</v>
-      </c>
-      <c r="I13" s="3" t="inlineStr"/>
+        <v>0.02995012297626834</v>
+      </c>
+      <c r="I13" s="4" t="n">
+        <v>0.07721887293914723</v>
+      </c>
+      <c r="J13" s="4" t="n">
+        <v>0.04188569563822661</v>
+      </c>
+      <c r="K13" s="4" t="n">
+        <v>0.007093646228126175</v>
+      </c>
+      <c r="L13" s="4" t="n">
+        <v>0.008286900605651988</v>
+      </c>
+      <c r="M13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" s="3" t="inlineStr"/>
     </row>
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>603128</t>
+          <t>600487</t>
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>-0.09831159999999993</v>
+        <v>0.4691076751072067</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.05582559999999998</v>
+        <v>0</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-0.02013609065739635</v>
+        <v>0.02100727259512307</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-0.0839894703611777</v>
+        <v>-0.1120115029152145</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.0393859568407999</v>
+        <v>0.1704571494730121</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.006888136600099408</v>
+        <v>-0.03191486429732198</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.002642252232442148</v>
-      </c>
-      <c r="I14" s="3" t="inlineStr"/>
+        <v>0.006139458940152109</v>
+      </c>
+      <c r="I14" s="4" t="n">
+        <v>0.2653910726211397</v>
+      </c>
+      <c r="J14" s="4" t="n">
+        <v>-0.109475716649378</v>
+      </c>
+      <c r="K14" s="4" t="n">
+        <v>0.18943168834764</v>
+      </c>
+      <c r="L14" s="4" t="n">
+        <v>0.06042549969546547</v>
+      </c>
+      <c r="M14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3" t="inlineStr"/>
     </row>
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
+          <t>600498</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="n">
+        <v>0.4466833649172879</v>
+      </c>
+      <c r="C15" s="4" t="n">
+        <v>0.000443380899529584</v>
+      </c>
+      <c r="D15" s="4" t="n">
+        <v>0.0183419676223141</v>
+      </c>
+      <c r="E15" s="4" t="n">
+        <v>0.03847945184033477</v>
+      </c>
+      <c r="F15" s="4" t="n">
+        <v>0.05310232241400954</v>
+      </c>
+      <c r="G15" s="4" t="n">
+        <v>0.004400703349238594</v>
+      </c>
+      <c r="H15" s="4" t="n">
+        <v>-0.08022335186870913</v>
+      </c>
+      <c r="I15" s="4" t="n">
+        <v>-0.05849509204296864</v>
+      </c>
+      <c r="J15" s="4" t="n">
+        <v>0.01297893874170786</v>
+      </c>
+      <c r="K15" s="4" t="n">
+        <v>0.1724060780364486</v>
+      </c>
+      <c r="L15" s="4" t="n">
+        <v>0.2172052983285326</v>
+      </c>
+      <c r="M15" s="4" t="n">
+        <v>0.03267714442070477</v>
+      </c>
+      <c r="N15" s="3" t="inlineStr"/>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>600517</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="n">
+        <v>0.2455061661011033</v>
+      </c>
+      <c r="C16" s="4" t="n">
+        <v>0.0004095267029864772</v>
+      </c>
+      <c r="D16" s="4" t="n">
+        <v>-0.07634516292535259</v>
+      </c>
+      <c r="E16" s="4" t="n">
+        <v>-0.1865749556744889</v>
+      </c>
+      <c r="F16" s="4" t="n">
+        <v>0.5938462636709694</v>
+      </c>
+      <c r="G16" s="4" t="n">
+        <v>-0.05362407791517687</v>
+      </c>
+      <c r="H16" s="4" t="n">
+        <v>0.03678073825039668</v>
+      </c>
+      <c r="I16" s="4" t="n">
+        <v>-0.06738419607294888</v>
+      </c>
+      <c r="J16" s="4" t="n">
+        <v>-0.01122845801912564</v>
+      </c>
+      <c r="K16" s="4" t="n">
+        <v>0.09674436036230048</v>
+      </c>
+      <c r="L16" s="4" t="n">
+        <v>0.04770651500073784</v>
+      </c>
+      <c r="M16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" s="3" t="inlineStr"/>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>600522</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="n">
+        <v>0.4619638269025763</v>
+      </c>
+      <c r="C17" s="4" t="n">
+        <v>-0.0005607543314973009</v>
+      </c>
+      <c r="D17" s="4" t="n">
+        <v>0.02698654427210177</v>
+      </c>
+      <c r="E17" s="4" t="n">
+        <v>-0.1368634299377036</v>
+      </c>
+      <c r="F17" s="4" t="n">
+        <v>0.08647657728685294</v>
+      </c>
+      <c r="G17" s="4" t="n">
+        <v>0.06378249863739509</v>
+      </c>
+      <c r="H17" s="4" t="n">
+        <v>0.3815262653080673</v>
+      </c>
+      <c r="I17" s="4" t="n">
+        <v>0.0428184187447218</v>
+      </c>
+      <c r="J17" s="4" t="n">
+        <v>-0.09994848161036821</v>
+      </c>
+      <c r="K17" s="4" t="n">
+        <v>0.05924179483087008</v>
+      </c>
+      <c r="L17" s="4" t="n">
+        <v>0.03951899869394628</v>
+      </c>
+      <c r="M17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" s="3" t="inlineStr"/>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>600531</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="n">
+        <v>0.7061901885467792</v>
+      </c>
+      <c r="C18" s="4" t="n">
+        <v>-0.006126628067365818</v>
+      </c>
+      <c r="D18" s="4" t="n">
+        <v>-0.001937709920766499</v>
+      </c>
+      <c r="E18" s="4" t="n">
+        <v>-0.1728250336493514</v>
+      </c>
+      <c r="F18" s="4" t="n">
+        <v>0.163831781899696</v>
+      </c>
+      <c r="G18" s="4" t="n">
+        <v>0.1199776629561216</v>
+      </c>
+      <c r="H18" s="4" t="n">
+        <v>0.09930383278012136</v>
+      </c>
+      <c r="I18" s="4" t="n">
+        <v>0.0001657312199296567</v>
+      </c>
+      <c r="J18" s="4" t="n">
+        <v>0.04645607722797915</v>
+      </c>
+      <c r="K18" s="4" t="n">
+        <v>0.2971356019635963</v>
+      </c>
+      <c r="L18" s="4" t="n">
+        <v>0.06892118822956468</v>
+      </c>
+      <c r="M18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" s="3" t="inlineStr"/>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>600875</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="n">
+        <v>0.521091276540333</v>
+      </c>
+      <c r="C19" s="4" t="n">
+        <v>0.007164680371626601</v>
+      </c>
+      <c r="D19" s="4" t="n">
+        <v>0.004714920004760534</v>
+      </c>
+      <c r="E19" s="4" t="n">
+        <v>-0.04486490442693132</v>
+      </c>
+      <c r="F19" s="4" t="n">
+        <v>0.0926967245068325</v>
+      </c>
+      <c r="G19" s="4" t="n">
+        <v>0.05333718627338412</v>
+      </c>
+      <c r="H19" s="4" t="n">
+        <v>0.1342709836150785</v>
+      </c>
+      <c r="I19" s="4" t="n">
+        <v>0.1127398549829628</v>
+      </c>
+      <c r="J19" s="4" t="n">
+        <v>-0.09723165181987077</v>
+      </c>
+      <c r="K19" s="4" t="n">
+        <v>0.06940287320132775</v>
+      </c>
+      <c r="L19" s="4" t="n">
+        <v>0.1221526505253729</v>
+      </c>
+      <c r="M19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" s="3" t="inlineStr"/>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>600887</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="n">
+        <v>0.2157300974143179</v>
+      </c>
+      <c r="C20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="4" t="n">
+        <v>-0.04916235709369184</v>
+      </c>
+      <c r="F20" s="4" t="n">
+        <v>0.1741098004285424</v>
+      </c>
+      <c r="G20" s="4" t="n">
+        <v>0.06397103951976311</v>
+      </c>
+      <c r="H20" s="4" t="n">
+        <v>0.0163937051620942</v>
+      </c>
+      <c r="I20" s="4" t="n">
+        <v>0.02158152342090961</v>
+      </c>
+      <c r="J20" s="4" t="n">
+        <v>-0.05485362973374836</v>
+      </c>
+      <c r="K20" s="4" t="n">
+        <v>0.0791350690617106</v>
+      </c>
+      <c r="L20" s="4" t="n">
+        <v>0.01264277512255047</v>
+      </c>
+      <c r="M20" s="4" t="n">
+        <v>-0.04560942936670475</v>
+      </c>
+      <c r="N20" s="3" t="inlineStr"/>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>600893</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="n">
+        <v>0.6316894995645821</v>
+      </c>
+      <c r="C21" s="4" t="n">
+        <v>0.0022988395812831</v>
+      </c>
+      <c r="D21" s="4" t="n">
+        <v>0.006185802616987578</v>
+      </c>
+      <c r="E21" s="4" t="n">
+        <v>-0.06394919328400218</v>
+      </c>
+      <c r="F21" s="4" t="n">
+        <v>0.07707225178651901</v>
+      </c>
+      <c r="G21" s="4" t="n">
+        <v>0.1561243978531529</v>
+      </c>
+      <c r="H21" s="4" t="n">
+        <v>0.2689073347023576</v>
+      </c>
+      <c r="I21" s="4" t="n">
+        <v>-0.05553922928833659</v>
+      </c>
+      <c r="J21" s="4" t="n">
+        <v>-0.03549537621253717</v>
+      </c>
+      <c r="K21" s="4" t="n">
+        <v>0.08535381375566682</v>
+      </c>
+      <c r="L21" s="4" t="n">
+        <v>0.07352980269385979</v>
+      </c>
+      <c r="M21" s="4" t="n">
+        <v>0.03064640522934292</v>
+      </c>
+      <c r="N21" s="3" t="inlineStr"/>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>601208</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="n">
+        <v>0.2350383108575851</v>
+      </c>
+      <c r="C22" s="4" t="n">
+        <v>0.007790621354217</v>
+      </c>
+      <c r="D22" s="4" t="n">
+        <v>-0.03350892189241166</v>
+      </c>
+      <c r="E22" s="4" t="n">
+        <v>-0.1293148407362052</v>
+      </c>
+      <c r="F22" s="4" t="n">
+        <v>0.2837228617678137</v>
+      </c>
+      <c r="G22" s="4" t="n">
+        <v>0.09003627110867338</v>
+      </c>
+      <c r="H22" s="4" t="n">
+        <v>0.02459676635388233</v>
+      </c>
+      <c r="I22" s="4" t="n">
+        <v>-0.08208696305838797</v>
+      </c>
+      <c r="J22" s="4" t="n">
+        <v>0.05231733042193233</v>
+      </c>
+      <c r="K22" s="4" t="n">
+        <v>-0.1278647175601228</v>
+      </c>
+      <c r="L22" s="4" t="n">
+        <v>0.2060013535565714</v>
+      </c>
+      <c r="M22" s="4" t="n">
+        <v>-0.0002164023011017287</v>
+      </c>
+      <c r="N22" s="3" t="inlineStr"/>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>603083</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="n">
+        <v>0.7955002268197202</v>
+      </c>
+      <c r="C23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="4" t="n">
+        <v>-0.005046636412172812</v>
+      </c>
+      <c r="F23" s="4" t="n">
+        <v>0.4157497381405835</v>
+      </c>
+      <c r="G23" s="4" t="n">
+        <v>-0.2247612395651387</v>
+      </c>
+      <c r="H23" s="4" t="n">
+        <v>0.07955918438917538</v>
+      </c>
+      <c r="I23" s="4" t="n">
+        <v>0.249487325505219</v>
+      </c>
+      <c r="J23" s="4" t="n">
+        <v>-0.1500107605761911</v>
+      </c>
+      <c r="K23" s="4" t="n">
+        <v>0.122155102539497</v>
+      </c>
+      <c r="L23" s="4" t="n">
+        <v>0.2700051249706849</v>
+      </c>
+      <c r="M23" s="4" t="n">
+        <v>0.006261067095092956</v>
+      </c>
+      <c r="N23" s="3" t="inlineStr"/>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>603128</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="n">
+        <v>0.01689762323912025</v>
+      </c>
+      <c r="C24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" s="4" t="n">
+        <v>0.02593719814565571</v>
+      </c>
+      <c r="E24" s="4" t="n">
+        <v>-0.1570250481661238</v>
+      </c>
+      <c r="F24" s="4" t="n">
+        <v>0.06048576370000788</v>
+      </c>
+      <c r="G24" s="4" t="n">
+        <v>0.1806068551060606</v>
+      </c>
+      <c r="H24" s="4" t="n">
+        <v>0.05782233916878076</v>
+      </c>
+      <c r="I24" s="4" t="n">
+        <v>-0.008975080595396282</v>
+      </c>
+      <c r="J24" s="4" t="n">
+        <v>-0.07698232011002883</v>
+      </c>
+      <c r="K24" s="4" t="n">
+        <v>-0.02496174790704724</v>
+      </c>
+      <c r="L24" s="4" t="n">
+        <v>-0.001595492303815538</v>
+      </c>
+      <c r="M24" s="4" t="n">
+        <v>-0.002997778657664919</v>
+      </c>
+      <c r="N24" s="3" t="inlineStr"/>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>603383</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="n">
+        <v>0.6286299662705359</v>
+      </c>
+      <c r="C25" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" s="4" t="n">
+        <v>0.003161718138807046</v>
+      </c>
+      <c r="E25" s="4" t="n">
+        <v>0.1102142532996483</v>
+      </c>
+      <c r="F25" s="4" t="n">
+        <v>0.354880857997332</v>
+      </c>
+      <c r="G25" s="4" t="n">
+        <v>-0.04451966610360364</v>
+      </c>
+      <c r="H25" s="4" t="n">
+        <v>0.1163590822920198</v>
+      </c>
+      <c r="I25" s="4" t="n">
+        <v>-0.05697571959246797</v>
+      </c>
+      <c r="J25" s="4" t="n">
+        <v>-0.03380015968898326</v>
+      </c>
+      <c r="K25" s="4" t="n">
+        <v>0.1037912766656055</v>
+      </c>
+      <c r="L25" s="4" t="n">
+        <v>0.01815657480706541</v>
+      </c>
+      <c r="M25" s="4" t="n">
+        <v>-0.01184166386113962</v>
+      </c>
+      <c r="N25" s="3" t="inlineStr"/>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
           <t>603496</t>
         </is>
       </c>
-      <c r="B15" s="4" t="n">
-        <v>1.5948434</v>
-      </c>
-      <c r="C15" s="4" t="n">
-        <v>0.0361725</v>
-      </c>
-      <c r="D15" s="4" t="n">
-        <v>0.2171775452446383</v>
-      </c>
-      <c r="E15" s="4" t="n">
-        <v>0.4721239410630732</v>
-      </c>
-      <c r="F15" s="4" t="n">
-        <v>0.1493037949935029</v>
-      </c>
-      <c r="G15" s="4" t="n">
-        <v>0.1871732236914713</v>
-      </c>
-      <c r="H15" s="4" t="n">
-        <v>0.02431103228242936</v>
-      </c>
-      <c r="I15" s="3" t="inlineStr"/>
+      <c r="B26" s="4" t="n">
+        <v>1.40568088737956</v>
+      </c>
+      <c r="C26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" s="4" t="n">
+        <v>0.00563715356855042</v>
+      </c>
+      <c r="E26" s="4" t="n">
+        <v>0.0571193856571815</v>
+      </c>
+      <c r="F26" s="4" t="n">
+        <v>0.2478454063605824</v>
+      </c>
+      <c r="G26" s="4" t="n">
+        <v>0.05305336658485477</v>
+      </c>
+      <c r="H26" s="4" t="n">
+        <v>0.0004221811971142412</v>
+      </c>
+      <c r="I26" s="4" t="n">
+        <v>0.1472376897622789</v>
+      </c>
+      <c r="J26" s="4" t="n">
+        <v>0.0536731619198734</v>
+      </c>
+      <c r="K26" s="4" t="n">
+        <v>0.151556948555246</v>
+      </c>
+      <c r="L26" s="4" t="n">
+        <v>0.1872658981152091</v>
+      </c>
+      <c r="M26" s="4" t="n">
+        <v>0.04156278543928115</v>
+      </c>
+      <c r="N26" s="3" t="inlineStr"/>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>603530</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="n">
+        <v>0.9960115835538752</v>
+      </c>
+      <c r="C27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="4" t="n">
+        <v>-4.782608695648377e-05</v>
+      </c>
+      <c r="G27" s="4" t="n">
+        <v>0.100877785629445</v>
+      </c>
+      <c r="H27" s="4" t="n">
+        <v>-0.03276865454646041</v>
+      </c>
+      <c r="I27" s="4" t="n">
+        <v>0.3196189492872211</v>
+      </c>
+      <c r="J27" s="4" t="n">
+        <v>0.1285664712651613</v>
+      </c>
+      <c r="K27" s="4" t="n">
+        <v>0.1182678312884525</v>
+      </c>
+      <c r="L27" s="4" t="n">
+        <v>0.1256226900681752</v>
+      </c>
+      <c r="M27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/socks_results_thresholds.xlsx
+++ b/socks_results_thresholds.xlsx
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N27"/>
+  <dimension ref="A1:J51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -462,11 +462,7 @@
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="20" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="25" customHeight="1">
@@ -482,60 +478,40 @@
       </c>
       <c r="C1" s="2" t="inlineStr">
         <is>
-          <t>2016年收益率</t>
+          <t>2020年收益率</t>
         </is>
       </c>
       <c r="D1" s="2" t="inlineStr">
         <is>
-          <t>2017年收益率</t>
+          <t>2021年收益率</t>
         </is>
       </c>
       <c r="E1" s="2" t="inlineStr">
         <is>
-          <t>2018年收益率</t>
+          <t>2022年收益率</t>
         </is>
       </c>
       <c r="F1" s="2" t="inlineStr">
         <is>
-          <t>2019年收益率</t>
+          <t>2023年收益率</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
         <is>
-          <t>2020年收益率</t>
+          <t>2024年收益率</t>
         </is>
       </c>
       <c r="H1" s="2" t="inlineStr">
         <is>
-          <t>2021年收益率</t>
+          <t>2025年收益率</t>
         </is>
       </c>
       <c r="I1" s="2" t="inlineStr">
         <is>
-          <t>2022年收益率</t>
-        </is>
-      </c>
-      <c r="J1" s="2" t="inlineStr">
-        <is>
-          <t>2023年收益率</t>
-        </is>
-      </c>
-      <c r="K1" s="2" t="inlineStr">
-        <is>
-          <t>2024年收益率</t>
-        </is>
-      </c>
-      <c r="L1" s="2" t="inlineStr">
-        <is>
-          <t>2025年收益率</t>
-        </is>
-      </c>
-      <c r="M1" s="2" t="inlineStr">
-        <is>
           <t>2026年收益率</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>gittag</t>
         </is>
@@ -548,1142 +524,1598 @@
         </is>
       </c>
       <c r="B2" s="4" t="n">
-        <v>-0.02688516057819335</v>
+        <v>-0.4258465991210982</v>
       </c>
       <c r="C2" s="4" t="n">
-        <v>-0.001229430484744371</v>
+        <v>0</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>0.1656643334342487</v>
+        <v>-0.1316296991315548</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>-0.003593012108475397</v>
+        <v>-0.009602563975472156</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>0.1140605089202705</v>
+        <v>-0.1875770567100138</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>0.04428120901698484</v>
+        <v>-0.01334402922569688</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>-0.0468806028697747</v>
+        <v>-0.1607619184823858</v>
       </c>
       <c r="I2" s="4" t="n">
-        <v>-0.0247695834862358</v>
-      </c>
-      <c r="J2" s="4" t="n">
-        <v>-0.180405286018933</v>
-      </c>
-      <c r="K2" s="4" t="n">
-        <v>0.05392040847239359</v>
-      </c>
-      <c r="L2" s="4" t="n">
-        <v>-0.1019503797811989</v>
-      </c>
-      <c r="M2" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" s="3" t="inlineStr"/>
+        <v>-0.007614609322071678</v>
+      </c>
+      <c r="J2" s="3" t="inlineStr"/>
     </row>
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>000519</t>
+          <t>000034</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>0.377496137029351</v>
+        <v>0.8177449487722008</v>
       </c>
       <c r="C3" s="4" t="n">
-        <v>0.01318246158557915</v>
+        <v>0.06454080269034748</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>-0.0952530584894674</v>
+        <v>0.04503550532516568</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>-0.1563864246971372</v>
+        <v>0.1013340266708192</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>0.205478441365287</v>
+        <v>0.08991023212722798</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>0.1465861162792758</v>
+        <v>0.1613126909664743</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>0.0271042607160982</v>
+        <v>0.2086094571874505</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>0.1379741129790851</v>
-      </c>
-      <c r="J3" s="4" t="n">
-        <v>-0.08908726175306908</v>
-      </c>
-      <c r="K3" s="4" t="n">
-        <v>0.04976037528529616</v>
-      </c>
-      <c r="L3" s="4" t="n">
-        <v>0.1138387274401325</v>
-      </c>
-      <c r="M3" s="4" t="n">
-        <v>0.0352130490992859</v>
-      </c>
-      <c r="N3" s="3" t="inlineStr"/>
+        <v>-0.03017217314786483</v>
+      </c>
+      <c r="J3" s="3" t="inlineStr"/>
     </row>
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>000977</t>
+          <t>000070</t>
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>1.143698460469436</v>
+        <v>-0.08329757125430548</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>-0.01494098093198118</v>
+        <v>0.0006772027985074965</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>0.01004849813436328</v>
+        <v>-0.1879712793763802</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0.111625921258592</v>
+        <v>0.04236020833224804</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>0.5171515276114548</v>
+        <v>0.2098928901105537</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>-0.105986385194218</v>
+        <v>-0.1432084620440754</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>0.1330178214616553</v>
+        <v>0.04405425780274429</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>-0.1018644865278034</v>
-      </c>
-      <c r="J4" s="4" t="n">
-        <v>0.03643743922935658</v>
-      </c>
-      <c r="K4" s="4" t="n">
-        <v>0.2353095035440132</v>
-      </c>
-      <c r="L4" s="4" t="n">
-        <v>0.1089321108997107</v>
-      </c>
-      <c r="M4" s="4" t="n">
-        <v>-0.01093458577464405</v>
-      </c>
-      <c r="N4" s="3" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="J4" s="3" t="inlineStr"/>
     </row>
     <row r="5" ht="20" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>002094</t>
+          <t>000533</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>-0.2290302956447963</v>
+        <v>1.265873406067317</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>0</v>
+        <v>0.02169971657218761</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>-0.1301937625754147</v>
+        <v>0.09478498224510976</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>-0.1838798414954443</v>
+        <v>0.3007413655866209</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>0.01404220477612879</v>
+        <v>0.09294199859903637</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>-0.08051915243196768</v>
+        <v>0.04379188561831912</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>0.09785830979487793</v>
+        <v>0.2408966985644501</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>0.03629962329816265</v>
-      </c>
-      <c r="J5" s="4" t="n">
-        <v>-0.02755302360837973</v>
-      </c>
-      <c r="K5" s="4" t="n">
-        <v>-0.05212087595361039</v>
-      </c>
-      <c r="L5" s="4" t="n">
-        <v>0.1246789207831454</v>
-      </c>
-      <c r="M5" s="4" t="n">
-        <v>-0.01239587949989335</v>
-      </c>
-      <c r="N5" s="3" t="inlineStr"/>
+        <v>0.1001348587216098</v>
+      </c>
+      <c r="J5" s="3" t="inlineStr"/>
     </row>
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>002432</t>
+          <t>000543</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>0.3110604900449792</v>
+        <v>1.138923339208232</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.003567645467814582</v>
+        <v>0.01328099268593825</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-0.1290132091389888</v>
+        <v>0.1511190657127207</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-0.1880559408811423</v>
+        <v>0.1618101815183016</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.1159530934774647</v>
+        <v>0.1840797399259725</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.06126171057603467</v>
+        <v>0.1984842169446597</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.5225839775838861</v>
+        <v>0.1122351825851565</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0.003203079575666372</v>
-      </c>
-      <c r="J6" s="4" t="n">
-        <v>-0.05280577633166925</v>
-      </c>
-      <c r="K6" s="4" t="n">
-        <v>0.06032220974427589</v>
-      </c>
-      <c r="L6" s="4" t="n">
-        <v>0.02405146832768522</v>
-      </c>
-      <c r="M6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" s="3" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="J6" s="3" t="inlineStr"/>
     </row>
     <row r="7" ht="20" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>002555</t>
+          <t>000977</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>-0.2188510394624068</v>
+        <v>0.2562502581162656</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>0</v>
+        <v>-0.1623492648462426</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.09099950751456025</v>
+        <v>0.181969870163562</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-0.2377656542307907</v>
+        <v>-0.133611950198829</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>0.2779628499867827</v>
+        <v>-0.002127316314337035</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.02543797340634396</v>
+        <v>0.2435802245653484</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.09961789237374166</v>
+        <v>0.2088281622647933</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-0.1035074899688088</v>
-      </c>
-      <c r="J7" s="4" t="n">
-        <v>-0.08671502997329111</v>
-      </c>
-      <c r="K7" s="4" t="n">
-        <v>-0.04581770165777979</v>
-      </c>
-      <c r="L7" s="4" t="n">
-        <v>0.07221502508590945</v>
-      </c>
-      <c r="M7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" s="3" t="inlineStr"/>
+        <v>-0.02370555121309333</v>
+      </c>
+      <c r="J7" s="3" t="inlineStr"/>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>002624</t>
+          <t>002094</t>
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>0.4268999207145161</v>
+        <v>0.2284643291289592</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-0.0284554010545573</v>
+        <v>-0.02032391572398191</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.09582701881215398</v>
+        <v>0.2382667583698769</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.005636468121785037</v>
+        <v>-0.03875433784916758</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.1344483265075544</v>
+        <v>-0.03493734601909897</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.1015726439376286</v>
+        <v>-0.09740103115074451</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.1108238055538835</v>
+        <v>0.2343297521330003</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>0.0704027897791301</v>
-      </c>
-      <c r="J8" s="4" t="n">
-        <v>-0.03811981024071829</v>
-      </c>
-      <c r="K8" s="4" t="n">
-        <v>-0.02329686757931304</v>
-      </c>
-      <c r="L8" s="4" t="n">
-        <v>0.1024858528982778</v>
-      </c>
-      <c r="M8" s="4" t="n">
-        <v>0.09409258056649271</v>
-      </c>
-      <c r="N8" s="3" t="inlineStr"/>
+        <v>-0.02017188480173754</v>
+      </c>
+      <c r="J8" s="3" t="inlineStr"/>
     </row>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>002714</t>
+          <t>002150</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>0.8926070977009466</v>
+        <v>0.5457578328049648</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.01066519190672829</v>
+        <v>0.005777368801540724</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>0.06766153381903181</v>
+        <v>0.08276826753165994</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.08031996929812378</v>
+        <v>0.5323756239156674</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.15982980424429</v>
+        <v>-0.07248278609564249</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.1288910218602991</v>
+        <v>-0.104033823839583</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.0999505012702567</v>
+        <v>0.114615938410437</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.0371147743460891</v>
-      </c>
-      <c r="J9" s="4" t="n">
-        <v>0.007062825395437806</v>
-      </c>
-      <c r="K9" s="4" t="n">
-        <v>0.03956762151624565</v>
-      </c>
-      <c r="L9" s="4" t="n">
-        <v>0.06696155756677309</v>
-      </c>
-      <c r="M9" s="4" t="n">
-        <v>-0.005907386072839737</v>
-      </c>
-      <c r="N9" s="3" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="J9" s="3" t="inlineStr"/>
     </row>
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>300454</t>
+          <t>002152</t>
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>0.1934996039077262</v>
+        <v>0.6092154712131064</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0</v>
+        <v>-0.07530140936074196</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0</v>
+        <v>0.2386790143176449</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.09097464452620072</v>
+        <v>0.02853965407862948</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.1655050880738232</v>
+        <v>0.08900562621995287</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.030559663258263</v>
+        <v>0.1634347752643391</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.04881845592860357</v>
+        <v>0.0855609309475843</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-0.1862046625158259</v>
-      </c>
-      <c r="J10" s="4" t="n">
-        <v>-0.1270161084898588</v>
-      </c>
-      <c r="K10" s="4" t="n">
-        <v>0.00357149884562849</v>
-      </c>
-      <c r="L10" s="4" t="n">
-        <v>0.316062217833205</v>
-      </c>
-      <c r="M10" s="4" t="n">
-        <v>0.02049463431685845</v>
-      </c>
-      <c r="N10" s="3" t="inlineStr"/>
+        <v>-0.006866081472449913</v>
+      </c>
+      <c r="J10" s="3" t="inlineStr"/>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>302132</t>
+          <t>002179</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>1.343704051553807</v>
+        <v>0.3327187094958826</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.004378971714252547</v>
+        <v>0</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-0.1288202016352762</v>
+        <v>0.2824304596366733</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-0.03806863730051115</v>
+        <v>0.004994028812352886</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.2956342080951972</v>
+        <v>-0.09993850004271637</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0.093663066087303</v>
+        <v>0.1103789743822605</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>0.08888623741099157</v>
+        <v>0.04251285075108282</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-0.1006717304009044</v>
-      </c>
-      <c r="J11" s="4" t="n">
-        <v>0.2614577983040718</v>
-      </c>
-      <c r="K11" s="4" t="n">
-        <v>0.2311750258341424</v>
-      </c>
-      <c r="L11" s="4" t="n">
-        <v>0.2873415630261882</v>
-      </c>
-      <c r="M11" s="4" t="n">
-        <v>0.01252046329634601</v>
-      </c>
-      <c r="N11" s="3" t="inlineStr"/>
+        <v>-0.00753235652946518</v>
+      </c>
+      <c r="J11" s="3" t="inlineStr"/>
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>600063</t>
+          <t>002261</t>
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>0.4326360890943335</v>
+        <v>1.704308598248176</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.01088949595447804</v>
+        <v>-0.05231483203393189</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-0.03884673095519597</v>
+        <v>0.1768157146974647</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.170216633932247</v>
+        <v>-0.03584287952341333</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.2692628084621347</v>
+        <v>0.1856029658638135</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.07089827004186536</v>
+        <v>0.01674453719110018</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0.2309421280662373</v>
+        <v>0.948230688805922</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.05715122761087535</v>
-      </c>
-      <c r="J12" s="4" t="n">
-        <v>-0.05593706866886022</v>
-      </c>
-      <c r="K12" s="4" t="n">
-        <v>0.06414145097815074</v>
-      </c>
-      <c r="L12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" s="3" t="inlineStr"/>
+        <v>0.07088882940703126</v>
+      </c>
+      <c r="J12" s="3" t="inlineStr"/>
     </row>
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>600089</t>
+          <t>002432</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>0.3042690707426874</v>
+        <v>0.6035706971969856</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0</v>
+        <v>-0.05262283174763929</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.01176426661526828</v>
+        <v>0.6002331743221975</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-0.05403457753494112</v>
+        <v>-0.0156355100527144</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.06755490035253181</v>
+        <v>-0.06967222020638979</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.08749726691733965</v>
+        <v>0.104658688597499</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0.02995012297626834</v>
+        <v>0.04559112291211608</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.07721887293914723</v>
-      </c>
-      <c r="J13" s="4" t="n">
-        <v>0.04188569563822661</v>
-      </c>
-      <c r="K13" s="4" t="n">
-        <v>0.007093646228126175</v>
-      </c>
-      <c r="L13" s="4" t="n">
-        <v>0.008286900605651988</v>
-      </c>
-      <c r="M13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" s="3" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="J13" s="3" t="inlineStr"/>
     </row>
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>600487</t>
+          <t>002459</t>
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>0.4691076751072067</v>
+        <v>0.2015453065267037</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>0</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.02100727259512307</v>
+        <v>0.3056366464825044</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-0.1120115029152145</v>
+        <v>0.173103330949345</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.1704571494730121</v>
+        <v>-0.1829313820995272</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.03191486429732198</v>
+        <v>-0.04432161229764322</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>0.006139458940152109</v>
+        <v>-0.03461222226680308</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.2653910726211397</v>
-      </c>
-      <c r="J14" s="4" t="n">
-        <v>-0.109475716649378</v>
-      </c>
-      <c r="K14" s="4" t="n">
-        <v>0.18943168834764</v>
-      </c>
-      <c r="L14" s="4" t="n">
-        <v>0.06042549969546547</v>
-      </c>
-      <c r="M14" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" s="3" t="inlineStr"/>
+        <v>0.04066143535069831</v>
+      </c>
+      <c r="J14" s="3" t="inlineStr"/>
     </row>
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>600498</t>
+          <t>002555</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>0.4466833649172879</v>
+        <v>-0.3555041559829664</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.000443380899529584</v>
+        <v>-0.09323298554046108</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.0183419676223141</v>
+        <v>-0.1027375328567596</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.03847945184033477</v>
+        <v>-0.1071163467734328</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.05310232241400954</v>
+        <v>-0.1337663060668707</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.004400703349238594</v>
+        <v>-0.0479485768888431</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.08022335186870913</v>
+        <v>0.07575792782223767</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.05849509204296864</v>
-      </c>
-      <c r="J15" s="4" t="n">
-        <v>0.01297893874170786</v>
-      </c>
-      <c r="K15" s="4" t="n">
-        <v>0.1724060780364486</v>
-      </c>
-      <c r="L15" s="4" t="n">
-        <v>0.2172052983285326</v>
-      </c>
-      <c r="M15" s="4" t="n">
-        <v>0.03267714442070477</v>
-      </c>
-      <c r="N15" s="3" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="J15" s="3" t="inlineStr"/>
     </row>
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>600517</t>
+          <t>002624</t>
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>0.2455061661011033</v>
+        <v>-0.02441990513827641</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.0004095267029864772</v>
+        <v>0.007061613278812147</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-0.07634516292535259</v>
+        <v>-0.1771375584465674</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-0.1865749556744889</v>
+        <v>0.05751293833747689</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.5938462636709694</v>
+        <v>-0.1072870880194241</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.05362407791517687</v>
+        <v>-0.06884697213289755</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>0.03678073825039668</v>
+        <v>0.1990913185756406</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-0.06738419607294888</v>
-      </c>
-      <c r="J16" s="4" t="n">
-        <v>-0.01122845801912564</v>
-      </c>
-      <c r="K16" s="4" t="n">
-        <v>0.09674436036230048</v>
-      </c>
-      <c r="L16" s="4" t="n">
-        <v>0.04770651500073784</v>
-      </c>
-      <c r="M16" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" s="3" t="inlineStr"/>
+        <v>0.1168859410208909</v>
+      </c>
+      <c r="J16" s="3" t="inlineStr"/>
     </row>
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>600522</t>
+          <t>002714</t>
         </is>
       </c>
       <c r="B17" s="4" t="n">
-        <v>0.4619638269025763</v>
+        <v>0.379096586663477</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.0005607543314973009</v>
+        <v>0.134811291021354</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.02698654427210177</v>
+        <v>0.08197007778252965</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-0.1368634299377036</v>
+        <v>0.02177072873705228</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.08647657728685294</v>
+        <v>-0.07798931443171522</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.06378249863739509</v>
+        <v>0.04286428767106865</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.3815262653080673</v>
+        <v>0.1262692148097309</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0.0428184187447218</v>
-      </c>
-      <c r="J17" s="4" t="n">
-        <v>-0.09994848161036821</v>
-      </c>
-      <c r="K17" s="4" t="n">
-        <v>0.05924179483087008</v>
-      </c>
-      <c r="L17" s="4" t="n">
-        <v>0.03951899869394628</v>
-      </c>
-      <c r="M17" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" s="3" t="inlineStr"/>
+        <v>0.01507086980180122</v>
+      </c>
+      <c r="J17" s="3" t="inlineStr"/>
     </row>
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>600531</t>
+          <t>300014</t>
         </is>
       </c>
       <c r="B18" s="4" t="n">
-        <v>0.7061901885467792</v>
+        <v>0.7312390105767459</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-0.006126628067365818</v>
+        <v>0</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-0.001937709920766499</v>
+        <v>0.5720680474617774</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-0.1728250336493514</v>
+        <v>0.07475109012689764</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.163831781899696</v>
+        <v>-0.3880220040009022</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0.1199776629561216</v>
+        <v>0.1524625376405654</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.09930383278012136</v>
+        <v>0.3956674982676155</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0.0001657312199296567</v>
-      </c>
-      <c r="J18" s="4" t="n">
-        <v>0.04645607722797915</v>
-      </c>
-      <c r="K18" s="4" t="n">
-        <v>0.2971356019635963</v>
-      </c>
-      <c r="L18" s="4" t="n">
-        <v>0.06892118822956468</v>
-      </c>
-      <c r="M18" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" s="3" t="inlineStr"/>
+        <v>0.04095799623875671</v>
+      </c>
+      <c r="J18" s="3" t="inlineStr"/>
     </row>
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>600875</t>
+          <t>300129</t>
         </is>
       </c>
       <c r="B19" s="4" t="n">
-        <v>0.521091276540333</v>
+        <v>1.977215898862412</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0.007164680371626601</v>
+        <v>0</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.004714920004760534</v>
+        <v>0.264568220419545</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-0.04486490442693132</v>
+        <v>0.1215743480020176</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.0926967245068325</v>
+        <v>0.354936156132921</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>0.05333718627338412</v>
+        <v>-0.05858374833637627</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>0.1342709836150785</v>
+        <v>0.2957734237964858</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0.1127398549829628</v>
-      </c>
-      <c r="J19" s="4" t="n">
-        <v>-0.09723165181987077</v>
-      </c>
-      <c r="K19" s="4" t="n">
-        <v>0.06940287320132775</v>
-      </c>
-      <c r="L19" s="4" t="n">
-        <v>0.1221526505253729</v>
-      </c>
-      <c r="M19" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" s="3" t="inlineStr"/>
+        <v>0.2700195511270025</v>
+      </c>
+      <c r="J19" s="3" t="inlineStr"/>
     </row>
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>600887</t>
+          <t>300207</t>
         </is>
       </c>
       <c r="B20" s="4" t="n">
-        <v>0.2157300974143179</v>
+        <v>0.1915559595042022</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>0</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0</v>
+        <v>0.2512545485892974</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-0.04916235709369184</v>
+        <v>-0.2449745543899451</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.1741098004285424</v>
+        <v>-0.1265753923989521</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.06397103951976311</v>
+        <v>0.1288869347195826</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.0163937051620942</v>
+        <v>0.2133084925171202</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>0.02158152342090961</v>
-      </c>
-      <c r="J20" s="4" t="n">
-        <v>-0.05485362973374836</v>
-      </c>
-      <c r="K20" s="4" t="n">
-        <v>0.0791350690617106</v>
-      </c>
-      <c r="L20" s="4" t="n">
-        <v>0.01264277512255047</v>
-      </c>
-      <c r="M20" s="4" t="n">
-        <v>-0.04560942936670475</v>
-      </c>
-      <c r="N20" s="3" t="inlineStr"/>
+        <v>0.05428997743272142</v>
+      </c>
+      <c r="J20" s="3" t="inlineStr"/>
     </row>
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>600893</t>
+          <t>300418</t>
         </is>
       </c>
       <c r="B21" s="4" t="n">
-        <v>0.6316894995645821</v>
+        <v>0.6055836896843039</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>0.0022988395812831</v>
+        <v>-0.1073768962501852</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>0.006185802616987578</v>
+        <v>0.1264637527889345</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-0.06394919328400218</v>
+        <v>-0.1346107599779747</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.07707225178651901</v>
+        <v>0.264107266054589</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>0.1561243978531529</v>
+        <v>0.08259716208549406</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0.2689073347023576</v>
+        <v>0.2623638339785719</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-0.05553922928833659</v>
-      </c>
-      <c r="J21" s="4" t="n">
-        <v>-0.03549537621253717</v>
-      </c>
-      <c r="K21" s="4" t="n">
-        <v>0.08535381375566682</v>
-      </c>
-      <c r="L21" s="4" t="n">
-        <v>0.07352980269385979</v>
-      </c>
-      <c r="M21" s="4" t="n">
-        <v>0.03064640522934292</v>
-      </c>
-      <c r="N21" s="3" t="inlineStr"/>
+        <v>0.06807255563314574</v>
+      </c>
+      <c r="J21" s="3" t="inlineStr"/>
     </row>
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>601208</t>
+          <t>300438</t>
         </is>
       </c>
       <c r="B22" s="4" t="n">
-        <v>0.2350383108575851</v>
+        <v>0.3449670231290745</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>0.007790621354217</v>
+        <v>0</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-0.03350892189241166</v>
+        <v>0.2052684740547588</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-0.1293148407362052</v>
+        <v>0.8280377249756695</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>0.2837228617678137</v>
+        <v>-0.5023146404093465</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>0.09003627110867338</v>
+        <v>0.03300285525111462</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0.02459676635388233</v>
+        <v>0.1254201339026276</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-0.08208696305838797</v>
-      </c>
-      <c r="J22" s="4" t="n">
-        <v>0.05231733042193233</v>
-      </c>
-      <c r="K22" s="4" t="n">
-        <v>-0.1278647175601228</v>
-      </c>
-      <c r="L22" s="4" t="n">
-        <v>0.2060013535565714</v>
-      </c>
-      <c r="M22" s="4" t="n">
-        <v>-0.0002164023011017287</v>
-      </c>
-      <c r="N22" s="3" t="inlineStr"/>
+        <v>0.05504653985414456</v>
+      </c>
+      <c r="J22" s="3" t="inlineStr"/>
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>603083</t>
+          <t>300454</t>
         </is>
       </c>
       <c r="B23" s="4" t="n">
-        <v>0.7955002268197202</v>
+        <v>0.1230397787113455</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>0</v>
+        <v>0.0620136625236155</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>0</v>
+        <v>-0.07421313614265374</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-0.005046636412172812</v>
+        <v>-0.2231319881223648</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>0.4157497381405835</v>
+        <v>-0.1285748396620877</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-0.2247612395651387</v>
+        <v>0.003608071790291716</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>0.07955918438917538</v>
+        <v>0.6242665416633529</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>0.249487325505219</v>
-      </c>
-      <c r="J23" s="4" t="n">
-        <v>-0.1500107605761911</v>
-      </c>
-      <c r="K23" s="4" t="n">
-        <v>0.122155102539497</v>
-      </c>
-      <c r="L23" s="4" t="n">
-        <v>0.2700051249706849</v>
-      </c>
-      <c r="M23" s="4" t="n">
-        <v>0.006261067095092956</v>
-      </c>
-      <c r="N23" s="3" t="inlineStr"/>
+        <v>0.03503549386572753</v>
+      </c>
+      <c r="J23" s="3" t="inlineStr"/>
     </row>
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>603128</t>
+          <t>300699</t>
         </is>
       </c>
       <c r="B24" s="4" t="n">
-        <v>0.01689762323912025</v>
+        <v>0.2657146985074017</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>0</v>
+        <v>0.07046758223563476</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>0.02593719814565571</v>
+        <v>0.1158899060979158</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-0.1570250481661238</v>
+        <v>-0.03438755826537955</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>0.06048576370000788</v>
+        <v>-0.2815573714087845</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>0.1806068551060606</v>
+        <v>0.1732013313153569</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>0.05782233916878076</v>
+        <v>0.210948377869438</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-0.008975080595396282</v>
-      </c>
-      <c r="J24" s="4" t="n">
-        <v>-0.07698232011002883</v>
-      </c>
-      <c r="K24" s="4" t="n">
-        <v>-0.02496174790704724</v>
-      </c>
-      <c r="L24" s="4" t="n">
-        <v>-0.001595492303815538</v>
-      </c>
-      <c r="M24" s="4" t="n">
-        <v>-0.002997778657664919</v>
-      </c>
-      <c r="N24" s="3" t="inlineStr"/>
+        <v>0.07509744957781041</v>
+      </c>
+      <c r="J24" s="3" t="inlineStr"/>
     </row>
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>603383</t>
+          <t>302132</t>
         </is>
       </c>
       <c r="B25" s="4" t="n">
-        <v>0.6286299662705359</v>
+        <v>1.11753603689438</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>0</v>
+        <v>0.05427907284701126</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>0.003161718138807046</v>
+        <v>0.07819287392511193</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>0.1102142532996483</v>
+        <v>-0.2199765136261269</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>0.354880857997332</v>
+        <v>0.2756298997906836</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-0.04451966610360364</v>
+        <v>0.3043348169558594</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>0.1163590822920198</v>
+        <v>0.5352997512983745</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-0.05697571959246797</v>
-      </c>
-      <c r="J25" s="4" t="n">
-        <v>-0.03380015968898326</v>
-      </c>
-      <c r="K25" s="4" t="n">
-        <v>0.1037912766656055</v>
-      </c>
-      <c r="L25" s="4" t="n">
-        <v>0.01815657480706541</v>
-      </c>
-      <c r="M25" s="4" t="n">
-        <v>-0.01184166386113962</v>
-      </c>
-      <c r="N25" s="3" t="inlineStr"/>
+        <v>-0.06510221563612328</v>
+      </c>
+      <c r="J25" s="3" t="inlineStr"/>
     </row>
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>603496</t>
+          <t>600063</t>
         </is>
       </c>
       <c r="B26" s="4" t="n">
-        <v>1.40568088737956</v>
+        <v>0.2226971875053056</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>0</v>
+        <v>0.02927971036051575</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>0.00563715356855042</v>
+        <v>0.1831906782892147</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>0.0571193856571815</v>
+        <v>0.09240144031067117</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>0.2478454063605824</v>
+        <v>-0.07448048918612216</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>0.05305336658485477</v>
+        <v>-0.006968741545798803</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>0.0004221811971142412</v>
+        <v>0</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>0.1472376897622789</v>
-      </c>
-      <c r="J26" s="4" t="n">
-        <v>0.0536731619198734</v>
-      </c>
-      <c r="K26" s="4" t="n">
-        <v>0.151556948555246</v>
-      </c>
-      <c r="L26" s="4" t="n">
-        <v>0.1872658981152091</v>
-      </c>
-      <c r="M26" s="4" t="n">
-        <v>0.04156278543928115</v>
-      </c>
-      <c r="N26" s="3" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="J26" s="3" t="inlineStr"/>
     </row>
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="3" t="inlineStr">
         <is>
+          <t>600089</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="n">
+        <v>0.4078860470437273</v>
+      </c>
+      <c r="C27" s="4" t="n">
+        <v>0.05195457157152734</v>
+      </c>
+      <c r="D27" s="4" t="n">
+        <v>0.05996764185084811</v>
+      </c>
+      <c r="E27" s="4" t="n">
+        <v>0.1367732281210556</v>
+      </c>
+      <c r="F27" s="4" t="n">
+        <v>0.07908795315388892</v>
+      </c>
+      <c r="G27" s="4" t="n">
+        <v>0.01350431109816096</v>
+      </c>
+      <c r="H27" s="4" t="n">
+        <v>0.01559751698670017</v>
+      </c>
+      <c r="I27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" s="3" t="inlineStr"/>
+    </row>
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>600157</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="n">
+        <v>0.5073990682672864</v>
+      </c>
+      <c r="C28" s="4" t="n">
+        <v>0.0258050858226823</v>
+      </c>
+      <c r="D28" s="4" t="n">
+        <v>0.2931092531299346</v>
+      </c>
+      <c r="E28" s="4" t="n">
+        <v>-0.02186726637508564</v>
+      </c>
+      <c r="F28" s="4" t="n">
+        <v>-0.04370364096206347</v>
+      </c>
+      <c r="G28" s="4" t="n">
+        <v>0.09368766843843743</v>
+      </c>
+      <c r="H28" s="4" t="n">
+        <v>0.1108222355562738</v>
+      </c>
+      <c r="I28" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" s="3" t="inlineStr"/>
+    </row>
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>600307</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="n">
+        <v>0.2350567959825018</v>
+      </c>
+      <c r="C29" s="4" t="n">
+        <v>0.02289405862851723</v>
+      </c>
+      <c r="D29" s="4" t="n">
+        <v>0.2575110639582328</v>
+      </c>
+      <c r="E29" s="4" t="n">
+        <v>-0.1836291615954542</v>
+      </c>
+      <c r="F29" s="4" t="n">
+        <v>-0.04301540167507592</v>
+      </c>
+      <c r="G29" s="4" t="n">
+        <v>0.01010321242010464</v>
+      </c>
+      <c r="H29" s="4" t="n">
+        <v>0.1703479010238221</v>
+      </c>
+      <c r="I29" s="4" t="n">
+        <v>0.03961202635151457</v>
+      </c>
+      <c r="J29" s="3" t="inlineStr"/>
+    </row>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>600330</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="n">
+        <v>0.4087625478011021</v>
+      </c>
+      <c r="C30" s="4" t="n">
+        <v>0.08190159609984402</v>
+      </c>
+      <c r="D30" s="4" t="n">
+        <v>-0.0008086068464367067</v>
+      </c>
+      <c r="E30" s="4" t="n">
+        <v>0.1072375929195315</v>
+      </c>
+      <c r="F30" s="4" t="n">
+        <v>0.01434014979444557</v>
+      </c>
+      <c r="G30" s="4" t="n">
+        <v>-0.02130265080343764</v>
+      </c>
+      <c r="H30" s="4" t="n">
+        <v>0.1694668061542125</v>
+      </c>
+      <c r="I30" s="4" t="n">
+        <v>0.01377272186630147</v>
+      </c>
+      <c r="J30" s="3" t="inlineStr"/>
+    </row>
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>600406</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="n">
+        <v>0.321201668411341</v>
+      </c>
+      <c r="C31" s="4" t="n">
+        <v>0.05305342061007293</v>
+      </c>
+      <c r="D31" s="4" t="n">
+        <v>0.07614477422754386</v>
+      </c>
+      <c r="E31" s="4" t="n">
+        <v>-0.01573302264918086</v>
+      </c>
+      <c r="F31" s="4" t="n">
+        <v>0.03343636898461527</v>
+      </c>
+      <c r="G31" s="4" t="n">
+        <v>0.1168038500246467</v>
+      </c>
+      <c r="H31" s="4" t="n">
+        <v>0.02630028825498389</v>
+      </c>
+      <c r="I31" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" s="3" t="inlineStr"/>
+    </row>
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>600410</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="n">
+        <v>0.2848754059198386</v>
+      </c>
+      <c r="C32" s="4" t="n">
+        <v>-0.2071970968042652</v>
+      </c>
+      <c r="D32" s="4" t="n">
+        <v>-0.1060972285215924</v>
+      </c>
+      <c r="E32" s="4" t="n">
+        <v>-0.06144217297078446</v>
+      </c>
+      <c r="F32" s="4" t="n">
+        <v>0.1037974874162273</v>
+      </c>
+      <c r="G32" s="4" t="n">
+        <v>-0.09300868811168093</v>
+      </c>
+      <c r="H32" s="4" t="n">
+        <v>0.5555816965915097</v>
+      </c>
+      <c r="I32" s="4" t="n">
+        <v>0.2403924447242157</v>
+      </c>
+      <c r="J32" s="3" t="inlineStr"/>
+    </row>
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>600487</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="n">
+        <v>0.5002235696124215</v>
+      </c>
+      <c r="C33" s="4" t="n">
+        <v>-0.0358336458234911</v>
+      </c>
+      <c r="D33" s="4" t="n">
+        <v>0.04511525795914971</v>
+      </c>
+      <c r="E33" s="4" t="n">
+        <v>0.2080089926765395</v>
+      </c>
+      <c r="F33" s="4" t="n">
+        <v>-0.1987379336193004</v>
+      </c>
+      <c r="G33" s="4" t="n">
+        <v>0.3814501707645569</v>
+      </c>
+      <c r="H33" s="4" t="n">
+        <v>0.1134221314540281</v>
+      </c>
+      <c r="I33" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" s="3" t="inlineStr"/>
+    </row>
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>600498</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="n">
+        <v>0.2117217774536229</v>
+      </c>
+      <c r="C34" s="4" t="n">
+        <v>-0.06948693880873091</v>
+      </c>
+      <c r="D34" s="4" t="n">
+        <v>-0.1526907003002803</v>
+      </c>
+      <c r="E34" s="4" t="n">
+        <v>-0.07799557576457551</v>
+      </c>
+      <c r="F34" s="4" t="n">
+        <v>0.005133070170213644</v>
+      </c>
+      <c r="G34" s="4" t="n">
+        <v>0.1055822073407681</v>
+      </c>
+      <c r="H34" s="4" t="n">
+        <v>0.4211578195301812</v>
+      </c>
+      <c r="I34" s="4" t="n">
+        <v>0.05547645516356496</v>
+      </c>
+      <c r="J34" s="3" t="inlineStr"/>
+    </row>
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>600517</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="n">
+        <v>0.1010919303133133</v>
+      </c>
+      <c r="C35" s="4" t="n">
+        <v>-0.03162995199957586</v>
+      </c>
+      <c r="D35" s="4" t="n">
+        <v>0.1390401688152468</v>
+      </c>
+      <c r="E35" s="4" t="n">
+        <v>-0.1209348504201973</v>
+      </c>
+      <c r="F35" s="4" t="n">
+        <v>-0.005832661467856629</v>
+      </c>
+      <c r="G35" s="4" t="n">
+        <v>0.04998144130563809</v>
+      </c>
+      <c r="H35" s="4" t="n">
+        <v>0.08788005582938772</v>
+      </c>
+      <c r="I35" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" s="3" t="inlineStr"/>
+    </row>
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>600522</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="n">
+        <v>0.5141620566705614</v>
+      </c>
+      <c r="C36" s="4" t="n">
+        <v>0.0183858671562899</v>
+      </c>
+      <c r="D36" s="4" t="n">
+        <v>0.4462189720833439</v>
+      </c>
+      <c r="E36" s="4" t="n">
+        <v>0.03765426005310474</v>
+      </c>
+      <c r="F36" s="4" t="n">
+        <v>-0.1030630713073345</v>
+      </c>
+      <c r="G36" s="4" t="n">
+        <v>0.06130484984392523</v>
+      </c>
+      <c r="H36" s="4" t="n">
+        <v>0.04080941819861771</v>
+      </c>
+      <c r="I36" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" s="3" t="inlineStr"/>
+    </row>
+    <row r="37" ht="20" customHeight="1">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>600531</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="n">
+        <v>1.09956942003754</v>
+      </c>
+      <c r="C37" s="4" t="n">
+        <v>0.06208342622307173</v>
+      </c>
+      <c r="D37" s="4" t="n">
+        <v>0.1872851920227262</v>
+      </c>
+      <c r="E37" s="4" t="n">
+        <v>-0.0005781794258750888</v>
+      </c>
+      <c r="F37" s="4" t="n">
+        <v>0.08354308405409606</v>
+      </c>
+      <c r="G37" s="4" t="n">
+        <v>0.3720237726152889</v>
+      </c>
+      <c r="H37" s="4" t="n">
+        <v>0.1206239697392773</v>
+      </c>
+      <c r="I37" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" s="3" t="inlineStr"/>
+    </row>
+    <row r="38" ht="20" customHeight="1">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>600732</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="n">
+        <v>1.007537915717376</v>
+      </c>
+      <c r="C38" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" s="4" t="n">
+        <v>0.1735572051045422</v>
+      </c>
+      <c r="E38" s="4" t="n">
+        <v>0.4430006864667891</v>
+      </c>
+      <c r="F38" s="4" t="n">
+        <v>-0.01401950045195803</v>
+      </c>
+      <c r="G38" s="4" t="n">
+        <v>-0.1457659571883889</v>
+      </c>
+      <c r="H38" s="4" t="n">
+        <v>0.299505898894659</v>
+      </c>
+      <c r="I38" s="4" t="n">
+        <v>0.08310235158734987</v>
+      </c>
+      <c r="J38" s="3" t="inlineStr"/>
+    </row>
+    <row r="39" ht="20" customHeight="1">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>600795</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="n">
+        <v>0.2056935635504871</v>
+      </c>
+      <c r="C39" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" s="4" t="n">
+        <v>0.0451581227761929</v>
+      </c>
+      <c r="E39" s="4" t="n">
+        <v>0.1136357277373088</v>
+      </c>
+      <c r="F39" s="4" t="n">
+        <v>0.02491712866188911</v>
+      </c>
+      <c r="G39" s="4" t="n">
+        <v>-0.03926387194901275</v>
+      </c>
+      <c r="H39" s="4" t="n">
+        <v>0.03428828207715469</v>
+      </c>
+      <c r="I39" s="4" t="n">
+        <v>0.01713197850931558</v>
+      </c>
+      <c r="J39" s="3" t="inlineStr"/>
+    </row>
+    <row r="40" ht="20" customHeight="1">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>600875</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="n">
+        <v>0.2910267854682198</v>
+      </c>
+      <c r="C40" s="4" t="n">
+        <v>0.015381649904144</v>
+      </c>
+      <c r="D40" s="4" t="n">
+        <v>0.2404202241634749</v>
+      </c>
+      <c r="E40" s="4" t="n">
+        <v>0.0708787503514284</v>
+      </c>
+      <c r="F40" s="4" t="n">
+        <v>-0.1801607829054755</v>
+      </c>
+      <c r="G40" s="4" t="n">
+        <v>0.06181899819746613</v>
+      </c>
+      <c r="H40" s="4" t="n">
+        <v>0.09955668290874063</v>
+      </c>
+      <c r="I40" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" s="3" t="inlineStr"/>
+    </row>
+    <row r="41" ht="20" customHeight="1">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>600887</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="n">
+        <v>0.00413883860270281</v>
+      </c>
+      <c r="C41" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D41" s="4" t="n">
+        <v>0.03019835617887351</v>
+      </c>
+      <c r="E41" s="4" t="n">
+        <v>-0.02637178743714757</v>
+      </c>
+      <c r="F41" s="4" t="n">
+        <v>-0.06817554360357309</v>
+      </c>
+      <c r="G41" s="4" t="n">
+        <v>0.09976017233869125</v>
+      </c>
+      <c r="H41" s="4" t="n">
+        <v>0.01563898044845754</v>
+      </c>
+      <c r="I41" s="4" t="n">
+        <v>-0.03814787306551133</v>
+      </c>
+      <c r="J41" s="3" t="inlineStr"/>
+    </row>
+    <row r="42" ht="20" customHeight="1">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>600893</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="n">
+        <v>0.694512680245146</v>
+      </c>
+      <c r="C42" s="4" t="n">
+        <v>0.118608137269989</v>
+      </c>
+      <c r="D42" s="4" t="n">
+        <v>0.2216270103809064</v>
+      </c>
+      <c r="E42" s="4" t="n">
+        <v>-0.0522650387008284</v>
+      </c>
+      <c r="F42" s="4" t="n">
+        <v>-0.06623926143425944</v>
+      </c>
+      <c r="G42" s="4" t="n">
+        <v>0.161534481428626</v>
+      </c>
+      <c r="H42" s="4" t="n">
+        <v>0.1371515298175529</v>
+      </c>
+      <c r="I42" s="4" t="n">
+        <v>0.0608531356424666</v>
+      </c>
+      <c r="J42" s="3" t="inlineStr"/>
+    </row>
+    <row r="43" ht="20" customHeight="1">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>601016</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="n">
+        <v>0.2505706402521821</v>
+      </c>
+      <c r="C43" s="4" t="n">
+        <v>0.06905714165112295</v>
+      </c>
+      <c r="D43" s="4" t="n">
+        <v>0.1185195737782735</v>
+      </c>
+      <c r="E43" s="4" t="n">
+        <v>-0.05673223348615358</v>
+      </c>
+      <c r="F43" s="4" t="n">
+        <v>-0.06255764051431323</v>
+      </c>
+      <c r="G43" s="4" t="n">
+        <v>0.04122625337224987</v>
+      </c>
+      <c r="H43" s="4" t="n">
+        <v>0.04294158519820255</v>
+      </c>
+      <c r="I43" s="4" t="n">
+        <v>0.08912834016055299</v>
+      </c>
+      <c r="J43" s="3" t="inlineStr"/>
+    </row>
+    <row r="44" ht="20" customHeight="1">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>601208</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="n">
+        <v>0.155744971162461</v>
+      </c>
+      <c r="C44" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" s="4" t="n">
+        <v>0.0492042563408424</v>
+      </c>
+      <c r="E44" s="4" t="n">
+        <v>-0.1445956060123627</v>
+      </c>
+      <c r="F44" s="4" t="n">
+        <v>0.05345075101264436</v>
+      </c>
+      <c r="G44" s="4" t="n">
+        <v>-0.1305116108924449</v>
+      </c>
+      <c r="H44" s="4" t="n">
+        <v>0.4064714243050523</v>
+      </c>
+      <c r="I44" s="4" t="n">
+        <v>-0.00041080043320451</v>
+      </c>
+      <c r="J44" s="3" t="inlineStr"/>
+    </row>
+    <row r="45" ht="20" customHeight="1">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>603083</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="n">
+        <v>-0.01967891313400982</v>
+      </c>
+      <c r="C45" s="4" t="n">
+        <v>-0.3138896842854599</v>
+      </c>
+      <c r="D45" s="4" t="n">
+        <v>0.0922782155079373</v>
+      </c>
+      <c r="E45" s="4" t="n">
+        <v>0.06655751531960863</v>
+      </c>
+      <c r="F45" s="4" t="n">
+        <v>-0.1955795421824252</v>
+      </c>
+      <c r="G45" s="4" t="n">
+        <v>0.1280938507019342</v>
+      </c>
+      <c r="H45" s="4" t="n">
+        <v>0.322245753571506</v>
+      </c>
+      <c r="I45" s="4" t="n">
+        <v>0.02215397844354682</v>
+      </c>
+      <c r="J45" s="3" t="inlineStr"/>
+    </row>
+    <row r="46" ht="20" customHeight="1">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>603128</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="n">
+        <v>-0.09904212528787193</v>
+      </c>
+      <c r="C46" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D46" s="4" t="n">
+        <v>0.1062191381486466</v>
+      </c>
+      <c r="E46" s="4" t="n">
+        <v>-0.09173095379911271</v>
+      </c>
+      <c r="F46" s="4" t="n">
+        <v>-0.07561672647844855</v>
+      </c>
+      <c r="G46" s="4" t="n">
+        <v>-0.02448272817729719</v>
+      </c>
+      <c r="H46" s="4" t="n">
+        <v>-0.001564106145644329</v>
+      </c>
+      <c r="I46" s="4" t="n">
+        <v>-0.004040732660303341</v>
+      </c>
+      <c r="J46" s="3" t="inlineStr"/>
+    </row>
+    <row r="47" ht="20" customHeight="1">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>603228</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="n">
+        <v>0.6992813142212695</v>
+      </c>
+      <c r="C47" s="4" t="n">
+        <v>-0.02990508919558706</v>
+      </c>
+      <c r="D47" s="4" t="n">
+        <v>0.1279488588168465</v>
+      </c>
+      <c r="E47" s="4" t="n">
+        <v>-0.1066439959475167</v>
+      </c>
+      <c r="F47" s="4" t="n">
+        <v>0.1461867503291611</v>
+      </c>
+      <c r="G47" s="4" t="n">
+        <v>0.2196763491987011</v>
+      </c>
+      <c r="H47" s="4" t="n">
+        <v>0.2789290744288351</v>
+      </c>
+      <c r="I47" s="4" t="n">
+        <v>-0.02772159677973569</v>
+      </c>
+      <c r="J47" s="3" t="inlineStr"/>
+    </row>
+    <row r="48" ht="20" customHeight="1">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>603383</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="n">
+        <v>-0.1797633640651194</v>
+      </c>
+      <c r="C48" s="4" t="n">
+        <v>-0.1666015320567743</v>
+      </c>
+      <c r="D48" s="4" t="n">
+        <v>0.08567167851536782</v>
+      </c>
+      <c r="E48" s="4" t="n">
+        <v>-0.05774793399240088</v>
+      </c>
+      <c r="F48" s="4" t="n">
+        <v>-0.06356641587204065</v>
+      </c>
+      <c r="G48" s="4" t="n">
+        <v>0.03603467561574532</v>
+      </c>
+      <c r="H48" s="4" t="n">
+        <v>0.03668265038608787</v>
+      </c>
+      <c r="I48" s="4" t="n">
+        <v>-0.04341458283319764</v>
+      </c>
+      <c r="J48" s="3" t="inlineStr"/>
+    </row>
+    <row r="49" ht="20" customHeight="1">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>603496</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="n">
+        <v>0.526286116492064</v>
+      </c>
+      <c r="C49" s="4" t="n">
+        <v>-0.1360368255351951</v>
+      </c>
+      <c r="D49" s="4" t="n">
+        <v>0.002426731990437832</v>
+      </c>
+      <c r="E49" s="4" t="n">
+        <v>0.01228627621758459</v>
+      </c>
+      <c r="F49" s="4" t="n">
+        <v>0.1073847370287029</v>
+      </c>
+      <c r="G49" s="4" t="n">
+        <v>0.07618266688069056</v>
+      </c>
+      <c r="H49" s="4" t="n">
+        <v>0.3859234357194435</v>
+      </c>
+      <c r="I49" s="4" t="n">
+        <v>0.05404940777022613</v>
+      </c>
+      <c r="J49" s="3" t="inlineStr"/>
+    </row>
+    <row r="50" ht="20" customHeight="1">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
           <t>603530</t>
         </is>
       </c>
-      <c r="B27" s="4" t="n">
-        <v>0.9960115835538752</v>
-      </c>
-      <c r="C27" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D27" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E27" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F27" s="4" t="n">
-        <v>-4.782608695648377e-05</v>
-      </c>
-      <c r="G27" s="4" t="n">
-        <v>0.100877785629445</v>
-      </c>
-      <c r="H27" s="4" t="n">
-        <v>-0.03276865454646041</v>
-      </c>
-      <c r="I27" s="4" t="n">
-        <v>0.3196189492872211</v>
-      </c>
-      <c r="J27" s="4" t="n">
-        <v>0.1285664712651613</v>
-      </c>
-      <c r="K27" s="4" t="n">
-        <v>0.1182678312884525</v>
-      </c>
-      <c r="L27" s="4" t="n">
-        <v>0.1256226900681752</v>
-      </c>
-      <c r="M27" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" s="3" t="inlineStr"/>
+      <c r="B50" s="4" t="n">
+        <v>1.101892030396975</v>
+      </c>
+      <c r="C50" s="4" t="n">
+        <v>0.0101768165406429</v>
+      </c>
+      <c r="D50" s="4" t="n">
+        <v>-0.1150726093959482</v>
+      </c>
+      <c r="E50" s="4" t="n">
+        <v>0.2727757510905062</v>
+      </c>
+      <c r="F50" s="4" t="n">
+        <v>0.2199157622245741</v>
+      </c>
+      <c r="G50" s="4" t="n">
+        <v>0.2401796046950968</v>
+      </c>
+      <c r="H50" s="4" t="n">
+        <v>0.221065745793707</v>
+      </c>
+      <c r="I50" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" s="3" t="inlineStr"/>
+    </row>
+    <row r="51" ht="20" customHeight="1">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>603606</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="n">
+        <v>0.933138903201234</v>
+      </c>
+      <c r="C51" s="4" t="n">
+        <v>0.053824723170379</v>
+      </c>
+      <c r="D51" s="4" t="n">
+        <v>0.3334716335528356</v>
+      </c>
+      <c r="E51" s="4" t="n">
+        <v>0.4436470541920511</v>
+      </c>
+      <c r="F51" s="4" t="n">
+        <v>-0.28164985004336</v>
+      </c>
+      <c r="G51" s="4" t="n">
+        <v>0.1027820180620862</v>
+      </c>
+      <c r="H51" s="4" t="n">
+        <v>0.1069205724788861</v>
+      </c>
+      <c r="I51" s="4" t="n">
+        <v>0.0866946914379671</v>
+      </c>
+      <c r="J51" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
